--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260818.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>11.04%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.60%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>86,925</t>
+          <t>34,155</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>8.09%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,155</t>
+          <t>86,925</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>8.06%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,095</t>
+          <t>108,266</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>108,266</t>
+          <t>47,095</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,631</t>
+          <t>131,101</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>131,101</t>
+          <t>21,631</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>48,160</t>
+          <t>31,310</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>31,310</t>
+          <t>48,160</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1107,66 +1107,66 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,937</t>
+          <t>29,245</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,458</t>
+          <t>10,937</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>29,245</t>
+          <t>21,458</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1188,24 +1188,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>45,227</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,44 +1217,44 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>45,227</t>
+          <t>19,909</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>19,909</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1474,117 +1474,117 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>12,924</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,527</t>
+          <t>12,924</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,527</t>
+          <t>5,678</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,678</t>
+          <t>90,902</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>90,902</t>
+          <t>6,527</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>149,115,416</t>
+          <t>117,154,074</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
